--- a/data/nzd0586/nzd0586.xlsx
+++ b/data/nzd0586/nzd0586.xlsx
@@ -20501,9 +20501,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0487</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -20551,9 +20557,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -20601,9 +20613,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1338</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -20651,9 +20669,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.09719999999999999</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -20701,9 +20725,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0617</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -20751,9 +20781,15 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -20801,9 +20837,15 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0503</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.1873</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -20851,9 +20893,15 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1465</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -20901,9 +20949,15 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.0438</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -20951,9 +21005,15 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1625</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -21001,9 +21061,15 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.09379999999999999</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1827</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -21051,9 +21117,15 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1707</v>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -21101,9 +21173,15 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -21151,9 +21229,15 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -21201,9 +21285,15 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0432</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1114</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -21251,9 +21341,15 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -21301,9 +21397,15 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -21351,9 +21453,15 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0448</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1135</v>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -21401,9 +21509,15 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -21451,9 +21565,15 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0397</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
